--- a/AAII_Financials/Yearly/SIM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SIM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>SIM</t>
   </si>
@@ -656,171 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F7" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G7" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>40543</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1716100</v>
+        <v>2433400</v>
       </c>
       <c r="E8" s="3">
-        <v>1791800</v>
+        <v>2776500</v>
       </c>
       <c r="F8" s="3">
-        <v>1441300</v>
+        <v>2713100</v>
       </c>
       <c r="G8" s="3">
+        <v>1802600</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1811700</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1815600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>1462000</v>
+      </c>
+      <c r="K8" s="3">
         <v>1381800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
         <v>1229200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="M8" s="3">
         <v>1347300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
         <v>1223800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
         <v>1328900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="P8" s="3">
         <v>1271100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="Q8" s="3">
         <v>1305000</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1510000</v>
+        <v>1839600</v>
       </c>
       <c r="E9" s="3">
-        <v>1534900</v>
+        <v>2034400</v>
       </c>
       <c r="F9" s="3">
-        <v>1205000</v>
+        <v>2025800</v>
       </c>
       <c r="G9" s="3">
+        <v>1531500</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1594100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1555300</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1222300</v>
+      </c>
+      <c r="K9" s="3">
         <v>1143800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="L9" s="3">
         <v>1159900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>1280200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>1125400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>1168500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>1150700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>1181400</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>206100</v>
+        <v>593800</v>
       </c>
       <c r="E10" s="3">
-        <v>256900</v>
+        <v>742100</v>
       </c>
       <c r="F10" s="3">
-        <v>236300</v>
+        <v>687300</v>
       </c>
       <c r="G10" s="3">
+        <v>271100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>217600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>260300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>239700</v>
+      </c>
+      <c r="K10" s="3">
         <v>238000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>69200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>67100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>98400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>160400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>120300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>123600</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +883,12 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -870,9 +922,21 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,9 +970,21 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -921,53 +997,65 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>104100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-9700</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>61700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>57300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>57800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>73000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>58800</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>56600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>74700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -978,9 +1066,21 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1092,108 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1599100</v>
+        <v>1983700</v>
       </c>
       <c r="E17" s="3">
-        <v>1588400</v>
+        <v>2156700</v>
       </c>
       <c r="F17" s="3">
-        <v>1266900</v>
+        <v>2053000</v>
       </c>
       <c r="G17" s="3">
+        <v>1542000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1688500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1609900</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1285100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1209800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
         <v>1334700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="M17" s="3">
         <v>1337100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>1184500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>1215600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>1210300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>1242600</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>117000</v>
+        <v>449700</v>
       </c>
       <c r="E18" s="3">
-        <v>203400</v>
+        <v>619800</v>
       </c>
       <c r="F18" s="3">
-        <v>174500</v>
+        <v>660100</v>
       </c>
       <c r="G18" s="3">
+        <v>260600</v>
+      </c>
+      <c r="H18" s="3">
+        <v>123200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>205800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>177000</v>
+      </c>
+      <c r="K18" s="3">
         <v>172100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="L18" s="3">
         <v>-105600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
         <v>10200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="N18" s="3">
         <v>39300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>113300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>60800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>62400</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1080,188 +1208,252 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-32100</v>
+        <v>140000</v>
       </c>
       <c r="E20" s="3">
-        <v>8300</v>
+        <v>75800</v>
       </c>
       <c r="F20" s="3">
-        <v>-30100</v>
+        <v>-15900</v>
       </c>
       <c r="G20" s="3">
+        <v>18300</v>
+      </c>
+      <c r="H20" s="3">
+        <v>41600</v>
+      </c>
+      <c r="I20" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>33300</v>
+      </c>
+      <c r="K20" s="3">
         <v>94600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="L20" s="3">
         <v>-17500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="M20" s="3">
         <v>25100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="N20" s="3">
         <v>-2300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="O20" s="3">
         <v>-21900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="P20" s="3">
         <v>-19700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="Q20" s="3">
         <v>-20200</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>140800</v>
+        <v>371400</v>
       </c>
       <c r="E21" s="3">
-        <v>267800</v>
+        <v>601300</v>
       </c>
       <c r="F21" s="3">
-        <v>218200</v>
+        <v>733800</v>
       </c>
       <c r="G21" s="3">
+        <v>315300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>140400</v>
+      </c>
+      <c r="I21" s="3">
+        <v>254900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>218300</v>
+      </c>
+      <c r="K21" s="3">
         <v>338700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="L21" s="3">
         <v>-59500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
         <v>91600</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I22" s="3">
+        <v>800</v>
+      </c>
+      <c r="J22" s="3">
         <v>2800</v>
       </c>
-      <c r="E22" s="3">
-        <v>800</v>
-      </c>
-      <c r="F22" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="M22" s="3">
         <v>1100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>82200</v>
+        <v>355700</v>
       </c>
       <c r="E23" s="3">
-        <v>210900</v>
+        <v>564000</v>
       </c>
       <c r="F23" s="3">
-        <v>141600</v>
+        <v>674900</v>
       </c>
       <c r="G23" s="3">
+        <v>245000</v>
+      </c>
+      <c r="H23" s="3">
+        <v>86800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>213700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>153700</v>
+      </c>
+      <c r="K23" s="3">
         <v>264600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="L23" s="3">
         <v>-125100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="M23" s="3">
         <v>34100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="N23" s="3">
         <v>35600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="O23" s="3">
         <v>90400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="P23" s="3">
         <v>40400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="Q23" s="3">
         <v>41500</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>164500</v>
+        <v>102900</v>
       </c>
       <c r="E24" s="3">
-        <v>37800</v>
+        <v>169200</v>
       </c>
       <c r="F24" s="3">
-        <v>55100</v>
+        <v>214100</v>
       </c>
       <c r="G24" s="3">
+        <v>104400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>173700</v>
+      </c>
+      <c r="I24" s="3">
+        <v>38300</v>
+      </c>
+      <c r="J24" s="3">
+        <v>57200</v>
+      </c>
+      <c r="K24" s="3">
         <v>46500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="L24" s="3">
         <v>38700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="M24" s="3">
         <v>8100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="N24" s="3">
         <v>-14100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="P24" s="3">
         <v>5800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="Q24" s="3">
         <v>6000</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1487,117 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-82400</v>
+        <v>252800</v>
       </c>
       <c r="E26" s="3">
-        <v>173100</v>
+        <v>394800</v>
       </c>
       <c r="F26" s="3">
-        <v>86500</v>
+        <v>460800</v>
       </c>
       <c r="G26" s="3">
+        <v>140600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-86900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>175400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>96500</v>
+      </c>
+      <c r="K26" s="3">
         <v>218100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="L26" s="3">
         <v>-163800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="M26" s="3">
         <v>26000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="N26" s="3">
         <v>49700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="O26" s="3">
         <v>87900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
         <v>34600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="Q26" s="3">
         <v>35500</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-82200</v>
+        <v>253300</v>
       </c>
       <c r="E27" s="3">
-        <v>183500</v>
+        <v>394900</v>
       </c>
       <c r="F27" s="3">
-        <v>86500</v>
+        <v>460700</v>
       </c>
       <c r="G27" s="3">
+        <v>140600</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-86700</v>
+      </c>
+      <c r="I27" s="3">
+        <v>185900</v>
+      </c>
+      <c r="J27" s="3">
+        <v>96500</v>
+      </c>
+      <c r="K27" s="3">
         <v>144900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="L27" s="3">
         <v>-61000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="M27" s="3">
         <v>60400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="N27" s="3">
         <v>76200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>93200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>29100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>29800</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,9 +1631,21 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1439,9 +1679,21 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1727,21 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1775,117 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>32100</v>
+        <v>-140000</v>
       </c>
       <c r="E32" s="3">
-        <v>-8300</v>
+        <v>-75800</v>
       </c>
       <c r="F32" s="3">
-        <v>30100</v>
+        <v>15900</v>
       </c>
       <c r="G32" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-94600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="L32" s="3">
         <v>17500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="M32" s="3">
         <v>-25100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="N32" s="3">
         <v>2300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="O32" s="3">
         <v>21900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="P32" s="3">
         <v>19700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="Q32" s="3">
         <v>20200</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-82200</v>
+        <v>253300</v>
       </c>
       <c r="E33" s="3">
-        <v>183500</v>
+        <v>394900</v>
       </c>
       <c r="F33" s="3">
-        <v>86500</v>
+        <v>460700</v>
       </c>
       <c r="G33" s="3">
+        <v>140600</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-86700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>185900</v>
+      </c>
+      <c r="J33" s="3">
+        <v>96500</v>
+      </c>
+      <c r="K33" s="3">
         <v>144900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="L33" s="3">
         <v>-61000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
         <v>60400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>76200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>93200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>29100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>29800</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1919,122 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-82200</v>
+        <v>253300</v>
       </c>
       <c r="E35" s="3">
-        <v>183500</v>
+        <v>394900</v>
       </c>
       <c r="F35" s="3">
-        <v>86500</v>
+        <v>460700</v>
       </c>
       <c r="G35" s="3">
+        <v>140600</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-86700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>185900</v>
+      </c>
+      <c r="J35" s="3">
+        <v>96500</v>
+      </c>
+      <c r="K35" s="3">
         <v>144900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="L35" s="3">
         <v>-61000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
         <v>60400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>76200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>93200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>29100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>29800</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F38" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G38" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>40543</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +2049,12 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,232 +2069,308 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>374000</v>
+        <v>1395000</v>
       </c>
       <c r="E41" s="3">
-        <v>350900</v>
+        <v>1104600</v>
       </c>
       <c r="F41" s="3">
-        <v>728000</v>
+        <v>738000</v>
       </c>
       <c r="G41" s="3">
+        <v>388400</v>
+      </c>
+      <c r="H41" s="3">
+        <v>394800</v>
+      </c>
+      <c r="I41" s="3">
+        <v>355600</v>
+      </c>
+      <c r="J41" s="3">
+        <v>367000</v>
+      </c>
+      <c r="K41" s="3">
         <v>400000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>312600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>351700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>350800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>365500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>338100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>179700</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>8500</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K42" s="3">
         <v>3700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>18800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>15300</v>
       </c>
-      <c r="J42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>713200</v>
+        <v>420900</v>
       </c>
       <c r="E43" s="3">
-        <v>799800</v>
+        <v>395100</v>
       </c>
       <c r="F43" s="3">
-        <v>1001000</v>
+        <v>360300</v>
       </c>
       <c r="G43" s="3">
+        <v>333800</v>
+      </c>
+      <c r="H43" s="3">
+        <v>422000</v>
+      </c>
+      <c r="I43" s="3">
+        <v>416100</v>
+      </c>
+      <c r="J43" s="3">
+        <v>346400</v>
+      </c>
+      <c r="K43" s="3">
         <v>523200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>198500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>185900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>155700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>123700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>191900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>176400</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>588400</v>
+        <v>603600</v>
       </c>
       <c r="E44" s="3">
-        <v>583200</v>
+        <v>655800</v>
       </c>
       <c r="F44" s="3">
-        <v>831000</v>
+        <v>573100</v>
       </c>
       <c r="G44" s="3">
+        <v>456000</v>
+      </c>
+      <c r="H44" s="3">
+        <v>437000</v>
+      </c>
+      <c r="I44" s="3">
+        <v>515900</v>
+      </c>
+      <c r="J44" s="3">
+        <v>421000</v>
+      </c>
+      <c r="K44" s="3">
         <v>500600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>306900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>327500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>595700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>281200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>297800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>285900</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>80200</v>
+        <v>49200</v>
       </c>
       <c r="E45" s="3">
-        <v>80200</v>
-      </c>
-      <c r="F45" s="3">
-        <v>47000</v>
+        <v>75900</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G45" s="3">
+        <v>42900</v>
+      </c>
+      <c r="H45" s="3">
+        <v>42300</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>38500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>16000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>7100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>18600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>10900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>10000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>13900</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1296100</v>
+        <v>2468700</v>
       </c>
       <c r="E46" s="3">
-        <v>1310800</v>
+        <v>2231300</v>
       </c>
       <c r="F46" s="3">
-        <v>1311200</v>
+        <v>1744900</v>
       </c>
       <c r="G46" s="3">
+        <v>1221100</v>
+      </c>
+      <c r="H46" s="3">
+        <v>1296200</v>
+      </c>
+      <c r="I46" s="3">
+        <v>1328300</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1164800</v>
+      </c>
+      <c r="K46" s="3">
         <v>1155400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>852700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>887500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>813600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>781300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>837800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>647200</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>78900</v>
+        <v>86500</v>
       </c>
       <c r="E47" s="3">
-        <v>117200</v>
+        <v>90200</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -1971,90 +2387,126 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1681100</v>
+        <v>1062000</v>
       </c>
       <c r="E48" s="3">
-        <v>1704500</v>
+        <v>860400</v>
       </c>
       <c r="F48" s="3">
-        <v>1580600</v>
+        <v>781100</v>
       </c>
       <c r="G48" s="3">
+        <v>801600</v>
+      </c>
+      <c r="H48" s="3">
+        <v>887400</v>
+      </c>
+      <c r="I48" s="3">
+        <v>863600</v>
+      </c>
+      <c r="J48" s="3">
+        <v>801700</v>
+      </c>
+      <c r="K48" s="3">
         <v>1455500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>558900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>684000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>103800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>441000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>483400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>502000</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>234500</v>
+        <v>132200</v>
       </c>
       <c r="E49" s="3">
-        <v>231000</v>
+        <v>115200</v>
       </c>
       <c r="F49" s="3">
-        <v>248200</v>
+        <v>110000</v>
       </c>
       <c r="G49" s="3">
+        <v>113100</v>
+      </c>
+      <c r="H49" s="3">
+        <v>119800</v>
+      </c>
+      <c r="I49" s="3">
+        <v>115600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>115900</v>
+      </c>
+      <c r="K49" s="3">
         <v>255500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>133100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>143700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>317300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>151300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>189400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>212100</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2540,21 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,45 +2588,69 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>48200</v>
+        <v>93700</v>
       </c>
       <c r="E52" s="3">
-        <v>57600</v>
+        <v>80300</v>
       </c>
       <c r="F52" s="3">
-        <v>61300</v>
+        <v>77400</v>
       </c>
       <c r="G52" s="3">
+        <v>64400</v>
+      </c>
+      <c r="H52" s="3">
+        <v>54900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>59900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>72200</v>
+      </c>
+      <c r="K52" s="3">
         <v>80200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>74600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>87500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>90900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>90500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>101000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>90900</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2684,69 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2302100</v>
+        <v>3950600</v>
       </c>
       <c r="E54" s="3">
-        <v>2453400</v>
+        <v>3467300</v>
       </c>
       <c r="F54" s="3">
-        <v>2286900</v>
+        <v>2797100</v>
       </c>
       <c r="G54" s="3">
+        <v>2283500</v>
+      </c>
+      <c r="H54" s="3">
+        <v>2441600</v>
+      </c>
+      <c r="I54" s="3">
+        <v>2486100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>2342100</v>
+      </c>
+      <c r="K54" s="3">
         <v>2091100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>1619300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>1802700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>1671300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>1464100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>1609500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>1452200</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2761,12 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,52 +2781,68 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>209900</v>
+        <v>455400</v>
       </c>
       <c r="E57" s="3">
-        <v>220500</v>
+        <v>498400</v>
       </c>
       <c r="F57" s="3">
-        <v>476300</v>
+        <v>352400</v>
       </c>
       <c r="G57" s="3">
+        <v>286400</v>
+      </c>
+      <c r="H57" s="3">
+        <v>234400</v>
+      </c>
+      <c r="I57" s="3">
+        <v>240500</v>
+      </c>
+      <c r="J57" s="3">
+        <v>215800</v>
+      </c>
+      <c r="K57" s="3">
         <v>142000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>155800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>183600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>151100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>135000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>155200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>148300</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12400</v>
+        <v>148100</v>
       </c>
       <c r="E58" s="3">
-        <v>17100</v>
+        <v>122400</v>
       </c>
       <c r="F58" s="3">
         <v>300</v>
@@ -2322,95 +2854,131 @@
         <v>300</v>
       </c>
       <c r="I58" s="3">
+        <v>300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>50300</v>
+      </c>
+      <c r="K58" s="3">
+        <v>300</v>
+      </c>
+      <c r="L58" s="3">
+        <v>300</v>
+      </c>
+      <c r="M58" s="3">
         <v>37800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>71700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>415700</v>
+        <v>70300</v>
       </c>
       <c r="E59" s="3">
-        <v>350000</v>
+        <v>107800</v>
       </c>
       <c r="F59" s="3">
-        <v>249900</v>
+        <v>107800</v>
       </c>
       <c r="G59" s="3">
+        <v>125900</v>
+      </c>
+      <c r="H59" s="3">
+        <v>141300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>18800</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K59" s="3">
         <v>185000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>124500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>70900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>77600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>33400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>42300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>58500</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>767200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>776900</v>
+      </c>
+      <c r="F60" s="3">
+        <v>539600</v>
+      </c>
+      <c r="G60" s="3">
+        <v>420500</v>
+      </c>
+      <c r="H60" s="3">
+        <v>494400</v>
+      </c>
+      <c r="I60" s="3">
         <v>457600</v>
       </c>
-      <c r="E60" s="3">
-        <v>451600</v>
-      </c>
-      <c r="F60" s="3">
-        <v>363400</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
+        <v>381000</v>
+      </c>
+      <c r="K60" s="3">
         <v>277200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>280600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>292300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>236300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>168600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>197700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>207000</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2444,45 +3012,69 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>236200</v>
+        <v>100</v>
       </c>
       <c r="E62" s="3">
-        <v>256700</v>
+        <v>4700</v>
       </c>
       <c r="F62" s="3">
-        <v>246000</v>
+        <v>10400</v>
       </c>
       <c r="G62" s="3">
+        <v>13000</v>
+      </c>
+      <c r="H62" s="3">
+        <v>31000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>38800</v>
+      </c>
+      <c r="J62" s="3">
+        <v>36600</v>
+      </c>
+      <c r="K62" s="3">
         <v>171600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>77100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>115300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>115500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>137700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>163700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>150400</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +3108,21 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +3156,21 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +3204,69 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>665700</v>
+        <v>1004500</v>
       </c>
       <c r="E66" s="3">
-        <v>653900</v>
+        <v>1006800</v>
       </c>
       <c r="F66" s="3">
-        <v>567800</v>
+        <v>758200</v>
       </c>
       <c r="G66" s="3">
+        <v>616000</v>
+      </c>
+      <c r="H66" s="3">
+        <v>712700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>679100</v>
+      </c>
+      <c r="J66" s="3">
+        <v>593900</v>
+      </c>
+      <c r="K66" s="3">
         <v>418000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>284800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>444800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>418500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>389800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>473400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>455300</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +3281,12 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +3320,21 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,9 +3368,21 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2748,9 +3416,21 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,45 +3464,69 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1151400</v>
+        <v>2507100</v>
       </c>
       <c r="E72" s="3">
-        <v>1241400</v>
+        <v>1953300</v>
       </c>
       <c r="F72" s="3">
-        <v>1130300</v>
+        <v>1475100</v>
       </c>
       <c r="G72" s="3">
+        <v>1053100</v>
+      </c>
+      <c r="H72" s="3">
+        <v>1059700</v>
+      </c>
+      <c r="I72" s="3">
+        <v>1100400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>1068200</v>
+      </c>
+      <c r="K72" s="3">
         <v>1056700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>890200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>959700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>1688100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>751600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>754700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>535300</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3560,21 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3608,21 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3656,69 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>1636400</v>
+        <v>2944600</v>
       </c>
       <c r="E76" s="3">
-        <v>1799500</v>
+        <v>2458600</v>
       </c>
       <c r="F76" s="3">
-        <v>1719100</v>
+        <v>2037000</v>
       </c>
       <c r="G76" s="3">
+        <v>1665700</v>
+      </c>
+      <c r="H76" s="3">
+        <v>1727600</v>
+      </c>
+      <c r="I76" s="3">
+        <v>1823500</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1753700</v>
+      </c>
+      <c r="K76" s="3">
         <v>1673100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>1334500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>1357900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>1252800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>1074300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>1136100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>996900</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3752,122 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F80" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G80" s="2">
+        <v>44196</v>
+      </c>
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>40543</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-82200</v>
+        <v>253300</v>
       </c>
       <c r="E81" s="3">
-        <v>183500</v>
+        <v>394900</v>
       </c>
       <c r="F81" s="3">
-        <v>86500</v>
+        <v>460700</v>
       </c>
       <c r="G81" s="3">
+        <v>140600</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-86700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>185900</v>
+      </c>
+      <c r="J81" s="3">
+        <v>96500</v>
+      </c>
+      <c r="K81" s="3">
         <v>144900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="L81" s="3">
         <v>-61000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
         <v>60400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>76200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>93200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>29100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>29800</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3882,60 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>55700</v>
+        <v>61200</v>
       </c>
       <c r="E83" s="3">
-        <v>55900</v>
+        <v>56700</v>
       </c>
       <c r="F83" s="3">
-        <v>73600</v>
+        <v>57300</v>
       </c>
       <c r="G83" s="3">
-        <v>71800</v>
+        <v>73000</v>
       </c>
       <c r="H83" s="3">
-        <v>63300</v>
+        <v>58300</v>
       </c>
       <c r="I83" s="3">
         <v>56100</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="J83" s="3">
+        <v>68300</v>
+      </c>
+      <c r="K83" s="3">
+        <v>71800</v>
+      </c>
+      <c r="L83" s="3">
+        <v>63300</v>
+      </c>
+      <c r="M83" s="3">
+        <v>56100</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3969,21 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +4017,21 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +4065,21 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +4113,21 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +4161,69 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>52400</v>
+        <v>252200</v>
       </c>
       <c r="E89" s="3">
-        <v>161900</v>
+        <v>450600</v>
       </c>
       <c r="F89" s="3">
-        <v>139200</v>
+        <v>409100</v>
       </c>
       <c r="G89" s="3">
+        <v>182600</v>
+      </c>
+      <c r="H89" s="3">
+        <v>55300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>164100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>162200</v>
+      </c>
+      <c r="K89" s="3">
         <v>172200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>-19200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>68800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>103000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>164500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>152800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>124500</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +4238,60 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-63900</v>
+        <v>-147400</v>
       </c>
       <c r="E91" s="3">
-        <v>-100200</v>
+        <v>-87000</v>
       </c>
       <c r="F91" s="3">
-        <v>-152600</v>
+        <v>-52000</v>
       </c>
       <c r="G91" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-67400</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-101500</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-154800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-155700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-32500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-93300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-159600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-58700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-22300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-26400</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +4325,21 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +4373,69 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5400</v>
+        <v>-75900</v>
       </c>
       <c r="E94" s="3">
-        <v>-41200</v>
+        <v>-212100</v>
       </c>
       <c r="F94" s="3">
-        <v>-135900</v>
+        <v>-49300</v>
       </c>
       <c r="G94" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-158900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-159000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-32900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-103500</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,8 +4450,12 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3537,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -3557,9 +4489,21 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +4537,21 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +4585,21 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,115 +4633,163 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-10600</v>
+        <v>-14400</v>
       </c>
       <c r="E100" s="3">
-        <v>-132700</v>
+        <v>114600</v>
       </c>
       <c r="F100" s="3">
-        <v>-18800</v>
+        <v>-7900</v>
       </c>
       <c r="G100" s="3">
+        <v>-104800</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-134400</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="K100" s="3">
         <v>45100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>-14300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-2400</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-13300</v>
+        <v>-41400</v>
       </c>
       <c r="E101" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>9100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-21800</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="I101" s="3">
         <v>1100</v>
       </c>
-      <c r="F101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K101" s="3">
         <v>7600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="L101" s="3">
         <v>30800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="M101" s="3">
         <v>38000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>23100</v>
+        <v>120500</v>
       </c>
       <c r="E102" s="3">
-        <v>-10900</v>
+        <v>328900</v>
       </c>
       <c r="F102" s="3">
-        <v>-16700</v>
+        <v>361100</v>
       </c>
       <c r="G102" s="3">
+        <v>14100</v>
+      </c>
+      <c r="H102" s="3">
+        <v>24300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="K102" s="3">
         <v>65900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-35600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-56100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>70500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>163000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>76300</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SIM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SIM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>SIM</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40543</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1615300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2433400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2776500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2713100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1802600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1811700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1815600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1462000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1381800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1229200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1347300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1223800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1328900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1271100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1305000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1222200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1839600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2034400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2025800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1531500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1594100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1555300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1222300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1143800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1159900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1280200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1125400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1168500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1150700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1181400</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E10" s="3">
         <v>593800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>742100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>687300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>271100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>217600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>260300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>239700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>238000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>69200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>98400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>160400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>120300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>123600</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,9 +998,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1000,66 +1019,69 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>-300</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
         <v>-300</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="J14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>104100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>-9700</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E15" s="3">
         <v>61700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>57300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>57800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>73000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>58800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>56600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>74700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1335500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1983700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2156700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2053000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1542000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1688500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1609900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1285100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1209800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1334700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1337100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1184500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1215600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1210300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1242600</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>279800</v>
+      </c>
+      <c r="E18" s="3">
         <v>449700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>619800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>660100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>260600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>123200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>205800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>177000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>172100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-105600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>39300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>113300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>60800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>62400</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,92 +1244,96 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-240800</v>
+      </c>
+      <c r="E20" s="3">
         <v>140000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>75800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-15900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>18300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>41600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>33300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>94600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-17500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-21900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-20200</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>570200</v>
+      </c>
+      <c r="E21" s="3">
         <v>371400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>601300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>733800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>315300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>140400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>254900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>218300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>338700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-59500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>91600</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1307,153 +1343,165 @@
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>9100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>2000</v>
       </c>
       <c r="L22" s="3">
         <v>2000</v>
       </c>
       <c r="M22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="N22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>598000</v>
+      </c>
+      <c r="E23" s="3">
         <v>355700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>564000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>674900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>245000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>86800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>213700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>153700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>264600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-125100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>34100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>35600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>90400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>40400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>41500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E24" s="3">
         <v>102900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>169200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>214100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>104400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>173700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>38300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>57200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>46500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>38700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-14100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>550600</v>
+      </c>
+      <c r="E26" s="3">
         <v>252800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>394800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>460800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>140600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-86900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>175400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>96500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>218100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-163800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>26000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>87900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>34600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>35500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>550700</v>
+      </c>
+      <c r="E27" s="3">
         <v>253300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>394900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>460700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>140600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-86700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>185900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>96500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>144900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-61000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>60400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>76200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>93200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>29100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>29800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>240800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-140000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-75800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>15900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-18300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-41600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-33300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-94600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>17500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>21900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>19700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>20200</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>550700</v>
+      </c>
+      <c r="E33" s="3">
         <v>253300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>394900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>460700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>140600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-86700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>185900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>96500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>144900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-61000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>60400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>76200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>93200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>29100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>29800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>550700</v>
+      </c>
+      <c r="E35" s="3">
         <v>253300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>394900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>460700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>140600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-86700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>185900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>96500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>144900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-61000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>60400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>76200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>93200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>29100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>29800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40543</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1399300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1395000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1104600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>738000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>388400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>394800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>355600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>367000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>400000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>312600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>351700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>350800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>365500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>338100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>179700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2145,20 +2234,20 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>4500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15300</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>8</v>
       </c>
@@ -2168,213 +2257,228 @@
       <c r="Q42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>414000</v>
+      </c>
+      <c r="E43" s="3">
         <v>420900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>395100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>360300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>333800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>422000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>416100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>346400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>523200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>198500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>185900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>155700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>123700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>191900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>176400</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>565400</v>
+      </c>
+      <c r="E44" s="3">
         <v>603600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>655800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>573100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>456000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>437000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>515900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>421000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>500600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>306900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>327500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>595700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>281200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>297800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>285900</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E45" s="3">
         <v>49200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>75900</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>42900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>38500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>18600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13900</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2398600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2468700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2231300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1744900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1221100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1296200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1328300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1164800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1155400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>852700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>887500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>813600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>781300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>837800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>647200</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E47" s="3">
         <v>86500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>90200</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2399,8 +2503,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -2408,105 +2512,114 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>942900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1062000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>860400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>781100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>801600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>887400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>863600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>801700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1455500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>558900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>684000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>103800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>441000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>483400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>502000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E49" s="3">
         <v>132200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>115200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>110000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>113100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>119800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>115600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>115900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>255500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>133100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>143700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>317300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>151300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>189400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>212100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E52" s="3">
         <v>93700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>80300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>77400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>64400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>54900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>59900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>72200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>80200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>74600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>87500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>90900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>90500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>101000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>90900</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3590100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3950600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3467300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2797100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2283500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2441600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2486100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2342100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2091100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1619300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1802700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1671300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1464100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1609500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1452200</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,67 +2914,71 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>218700</v>
+      </c>
+      <c r="E57" s="3">
         <v>455400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>498400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>352400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>286400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>234400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>240500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>215800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>142000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>155800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>183600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>151100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>135000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>155200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>148300</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3">
         <v>148100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>122400</v>
-      </c>
-      <c r="F58" s="3">
-        <v>300</v>
       </c>
       <c r="G58" s="3">
         <v>300</v>
@@ -2857,22 +2990,22 @@
         <v>300</v>
       </c>
       <c r="J58" s="3">
+        <v>300</v>
+      </c>
+      <c r="K58" s="3">
         <v>50300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>300</v>
       </c>
       <c r="L58" s="3">
         <v>300</v>
       </c>
       <c r="M58" s="3">
+        <v>300</v>
+      </c>
+      <c r="N58" s="3">
         <v>37800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>71700</v>
-      </c>
-      <c r="O58" s="3">
-        <v>200</v>
       </c>
       <c r="P58" s="3">
         <v>200</v>
@@ -2880,105 +3013,114 @@
       <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>200</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E59" s="3">
         <v>70300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>107800</v>
       </c>
       <c r="F59" s="3">
         <v>107800</v>
       </c>
       <c r="G59" s="3">
+        <v>107800</v>
+      </c>
+      <c r="H59" s="3">
         <v>125900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>141300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>185000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>124500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>33400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>58500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>559600</v>
+      </c>
+      <c r="E60" s="3">
         <v>767200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>776900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>539600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>420500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>494400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>457600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>381000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>277200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>280600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>292300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>236300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>168600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>197700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>207000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3024,57 +3166,63 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>36600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>171600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>77100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>115300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>115500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>137700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>163700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>150400</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>749200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1004500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1006800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>758200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>616000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>712700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>679100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>593900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>418000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>284800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>444800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>418500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>389800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>473400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>455300</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2920700</v>
+      </c>
+      <c r="E72" s="3">
         <v>2507100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1953300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1475100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1053100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1059700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1100400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1068200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1056700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>890200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>959700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1688100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>751600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>754700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>535300</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2839800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2944600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2458600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2037000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1665700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1727600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1823500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1753700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1673100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1334500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1357900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1252800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1074300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1136100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>996900</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40543</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>550700</v>
+      </c>
+      <c r="E81" s="3">
         <v>253300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>394900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>460700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>140600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-86700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>185900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>96500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>144900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-61000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>60400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>76200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>93200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>29100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>29800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,44 +4083,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E83" s="3">
         <v>61200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>56700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>57300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>73000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>58300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>56100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>68300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>71800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>63300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>56100</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
@@ -3933,9 +4131,12 @@
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>265900</v>
+      </c>
+      <c r="E89" s="3">
         <v>252200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>450600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>409100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>182600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>55300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>164100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>162200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>172200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>68800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>103000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>164500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>152800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>124500</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-101700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-147400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-87000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-47800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-67400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-101500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-154800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-155700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-93300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-159600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-58700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,45 +4611,48 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-75900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-212100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-49300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-41800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-41700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-158900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-159000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-32900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-103500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
@@ -4433,9 +4662,12 @@
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,8 +4686,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4469,11 +4702,11 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>100000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -4501,9 +4734,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,45 +4887,48 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>114600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-104800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-134400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-19100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>45100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2400</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
@@ -4693,45 +4938,48 @@
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-41400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-24100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-21800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-14100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>30800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>38000</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
@@ -4741,55 +4989,61 @@
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>267400</v>
+      </c>
+      <c r="E102" s="3">
         <v>120500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>328900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>361100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>24300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>65900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-35600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-56100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>70500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>163000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>76300</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SIM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SIM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>SIM</t>
   </si>
@@ -783,7 +783,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1222200</v>
+        <v>1249300</v>
       </c>
       <c r="E9" s="3">
         <v>1839600</v>
@@ -834,7 +834,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>393000</v>
+        <v>365900</v>
       </c>
       <c r="E10" s="3">
         <v>593800</v>
@@ -1059,10 +1059,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>49600</v>
+        <v>51200</v>
       </c>
       <c r="E15" s="3">
-        <v>61700</v>
+        <v>61200</v>
       </c>
       <c r="F15" s="3">
         <v>57300</v>
@@ -1128,7 +1128,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1335500</v>
+        <v>1360900</v>
       </c>
       <c r="E17" s="3">
         <v>1983700</v>
@@ -1179,7 +1179,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>279800</v>
+        <v>254400</v>
       </c>
       <c r="E18" s="3">
         <v>449700</v>
@@ -1251,13 +1251,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-240800</v>
+        <v>-269900</v>
       </c>
       <c r="E20" s="3">
         <v>140000</v>
       </c>
       <c r="F20" s="3">
-        <v>75800</v>
+        <v>67600</v>
       </c>
       <c r="G20" s="3">
         <v>-15900</v>
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>570200</v>
+        <v>575500</v>
       </c>
       <c r="E21" s="3">
-        <v>371400</v>
+        <v>370900</v>
       </c>
       <c r="F21" s="3">
-        <v>601300</v>
+        <v>609400</v>
       </c>
       <c r="G21" s="3">
         <v>733800</v>
@@ -1404,13 +1404,13 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>598000</v>
+        <v>601800</v>
       </c>
       <c r="E23" s="3">
         <v>355700</v>
       </c>
       <c r="F23" s="3">
-        <v>564000</v>
+        <v>572200</v>
       </c>
       <c r="G23" s="3">
         <v>674900</v>
@@ -1455,7 +1455,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>47400</v>
+        <v>98900</v>
       </c>
       <c r="E24" s="3">
         <v>102900</v>
@@ -1557,13 +1557,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>550600</v>
+        <v>503000</v>
       </c>
       <c r="E26" s="3">
         <v>252800</v>
       </c>
       <c r="F26" s="3">
-        <v>394800</v>
+        <v>403000</v>
       </c>
       <c r="G26" s="3">
         <v>460800</v>
@@ -1608,13 +1608,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>550700</v>
+        <v>503300</v>
       </c>
       <c r="E27" s="3">
         <v>253300</v>
       </c>
       <c r="F27" s="3">
-        <v>394900</v>
+        <v>403100</v>
       </c>
       <c r="G27" s="3">
         <v>460700</v>
@@ -1863,13 +1863,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>240800</v>
+        <v>269900</v>
       </c>
       <c r="E32" s="3">
         <v>-140000</v>
       </c>
       <c r="F32" s="3">
-        <v>-75800</v>
+        <v>-67600</v>
       </c>
       <c r="G32" s="3">
         <v>15900</v>
@@ -1914,13 +1914,13 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>550700</v>
+        <v>503300</v>
       </c>
       <c r="E33" s="3">
         <v>253300</v>
       </c>
       <c r="F33" s="3">
-        <v>394900</v>
+        <v>403100</v>
       </c>
       <c r="G33" s="3">
         <v>460700</v>
@@ -2016,13 +2016,13 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>550700</v>
+        <v>503300</v>
       </c>
       <c r="E35" s="3">
         <v>253300</v>
       </c>
       <c r="F35" s="3">
-        <v>394900</v>
+        <v>403100</v>
       </c>
       <c r="G35" s="3">
         <v>460700</v>
@@ -2267,7 +2267,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>414000</v>
+        <v>273600</v>
       </c>
       <c r="E43" s="3">
         <v>420900</v>
@@ -2318,7 +2318,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>565400</v>
+        <v>535800</v>
       </c>
       <c r="E44" s="3">
         <v>603600</v>
@@ -2368,11 +2368,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>19800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>49200</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
         <v>75900</v>
@@ -2420,7 +2420,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2398600</v>
+        <v>2230000</v>
       </c>
       <c r="E46" s="3">
         <v>2468700</v>
@@ -2522,7 +2522,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>942900</v>
+        <v>942100</v>
       </c>
       <c r="E48" s="3">
         <v>1062000</v>
@@ -2573,7 +2573,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>108500</v>
+        <v>108200</v>
       </c>
       <c r="E49" s="3">
         <v>132200</v>
@@ -2726,7 +2726,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>75900</v>
+        <v>81500</v>
       </c>
       <c r="E52" s="3">
         <v>93700</v>
@@ -2828,7 +2828,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>3590100</v>
+        <v>3517600</v>
       </c>
       <c r="E54" s="3">
         <v>3950600</v>
@@ -2921,7 +2921,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>218700</v>
+        <v>212700</v>
       </c>
       <c r="E57" s="3">
         <v>455400</v>
@@ -2972,7 +2972,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>300</v>
+        <v>152700</v>
       </c>
       <c r="E58" s="3">
         <v>148100</v>
@@ -3023,7 +3023,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>218500</v>
+        <v>56200</v>
       </c>
       <c r="E59" s="3">
         <v>70300</v>
@@ -3074,7 +3074,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>559600</v>
+        <v>489500</v>
       </c>
       <c r="E60" s="3">
         <v>767200</v>
@@ -3176,7 +3176,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
@@ -3380,7 +3380,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>749200</v>
+        <v>674600</v>
       </c>
       <c r="E66" s="3">
         <v>1004500</v>
@@ -3656,7 +3656,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2920700</v>
+        <v>2537400</v>
       </c>
       <c r="E72" s="3">
         <v>2507100</v>
@@ -3860,7 +3860,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2839800</v>
+        <v>2841700</v>
       </c>
       <c r="E76" s="3">
         <v>2944600</v>
@@ -4018,13 +4018,13 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>550700</v>
+        <v>503300</v>
       </c>
       <c r="E81" s="3">
         <v>253300</v>
       </c>
       <c r="F81" s="3">
-        <v>394900</v>
+        <v>403100</v>
       </c>
       <c r="G81" s="3">
         <v>460700</v>
@@ -4090,13 +4090,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>49600</v>
+        <v>51200</v>
       </c>
       <c r="E83" s="3">
         <v>61200</v>
       </c>
       <c r="F83" s="3">
-        <v>56700</v>
+        <v>57300</v>
       </c>
       <c r="G83" s="3">
         <v>57300</v>
@@ -4396,13 +4396,13 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>265900</v>
+        <v>266300</v>
       </c>
       <c r="E89" s="3">
         <v>252200</v>
       </c>
       <c r="F89" s="3">
-        <v>450600</v>
+        <v>458800</v>
       </c>
       <c r="G89" s="3">
         <v>409100</v>
@@ -4468,7 +4468,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-101700</v>
+        <v>-102100</v>
       </c>
       <c r="E91" s="3">
         <v>-147400</v>
@@ -4621,7 +4621,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-13000</v>
+        <v>-13300</v>
       </c>
       <c r="E94" s="3">
         <v>-75900</v>
@@ -4954,7 +4954,7 @@
         <v>-41400</v>
       </c>
       <c r="F101" s="3">
-        <v>-24100</v>
+        <v>-32300</v>
       </c>
       <c r="G101" s="3">
         <v>9100</v>
@@ -4999,7 +4999,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>267400</v>
+        <v>267500</v>
       </c>
       <c r="E102" s="3">
         <v>120500</v>
